--- a/surveyor_forms/011_household_beverage_container_survey--surveyor_forms.xlsx
+++ b/surveyor_forms/011_household_beverage_container_survey--surveyor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'contact_info_option_1',_'value':_'contact_info_option_1'}</t>
+          <t>contact_info_option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'contact_info_option_1', 'value': 'contact_info_option_1'}</t>
+          <t>contact info option 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'contact_info_option_2',_'value':_'contact_info_option_2'}</t>
+          <t>contact_info_option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'contact_info_option_2', 'value': 'contact_info_option_2'}</t>
+          <t>contact info option 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contact_info_option_3',_'value':_'contact_info_option_3'}</t>
+          <t>contact_info_option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'contact_info_option_3', 'value': 'contact_info_option_3'}</t>
+          <t>contact info option 3</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'household_beverage_container_type_1',_'value':_'household_beverage_container_type_1'}</t>
+          <t>household_beverage_container_type_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'household_beverage_container_type_1', 'value': 'household_beverage_container_type_1'}</t>
+          <t>household beverage container type 1</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'household_beverage_container_type_2',_'value':_'household_beverage_container_type_2'}</t>
+          <t>household_beverage_container_type_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'household_beverage_container_type_2', 'value': 'household_beverage_container_type_2'}</t>
+          <t>household beverage container type 2</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'household_beverage_container_type_3',_'value':_'household_beverage_container_type_3'}</t>
+          <t>household_beverage_container_type_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'household_beverage_container_type_3', 'value': 'household_beverage_container_type_3'}</t>
+          <t>household beverage container type 3</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'household_beverage_container_content_1',_'value':_'household_beverage_container_content_1'}</t>
+          <t>household_beverage_container_content_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'household_beverage_container_content_1', 'value': 'household_beverage_container_content_1'}</t>
+          <t>household beverage container content 1</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'household_beverage_container_content_2',_'value':_'household_beverage_container_content_2'}</t>
+          <t>household_beverage_container_content_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'household_beverage_container_content_2', 'value': 'household_beverage_container_content_2'}</t>
+          <t>household beverage container content 2</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'household_beverage_container_content_3',_'value':_'household_beverage_container_content_3'}</t>
+          <t>household_beverage_container_content_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'household_beverage_container_content_3', 'value': 'household_beverage_container_content_3'}</t>
+          <t>household beverage container content 3</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'household_beverage_container_shape_1',_'value':_'household_beverage_container_shape_1'}</t>
+          <t>household_beverage_container_shape_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'household_beverage_container_shape_1', 'value': 'household_beverage_container_shape_1'}</t>
+          <t>household beverage container shape 1</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'household_beverage_container_shape_2',_'value':_'household_beverage_container_shape_2'}</t>
+          <t>household_beverage_container_shape_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'household_beverage_container_shape_2', 'value': 'household_beverage_container_shape_2'}</t>
+          <t>household beverage container shape 2</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'household_beverage_container_shape_3',_'value':_'household_beverage_container_shape_3'}</t>
+          <t>household_beverage_container_shape_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'household_beverage_container_shape_3', 'value': 'household_beverage_container_shape_3'}</t>
+          <t>household beverage container shape 3</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'household_beverage_container_material_1',_'value':_'household_beverage_container_material_1'}</t>
+          <t>household_beverage_container_material_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'household_beverage_container_material_1', 'value': 'household_beverage_container_material_1'}</t>
+          <t>household beverage container material 1</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'household_beverage_container_material_2',_'value':_'household_beverage_container_material_2'}</t>
+          <t>household_beverage_container_material_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'household_beverage_container_material_2', 'value': 'household_beverage_container_material_2'}</t>
+          <t>household beverage container material 2</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'household_beverage_container_material_3',_'value':_'household_beverage_container_material_3'}</t>
+          <t>household_beverage_container_material_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'household_beverage_container_material_3', 'value': 'household_beverage_container_material_3'}</t>
+          <t>household beverage container material 3</t>
         </is>
       </c>
     </row>
